--- a/CAPACITORGOODpuget/project/Post Verilog Run Checks.xlsx
+++ b/CAPACITORGOODpuget/project/Post Verilog Run Checks.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="70">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -88,49 +88,49 @@
     <t>(!!! MUST FIX !!! - not allowed)</t>
   </si>
   <si>
+    <t>Floating pin V_GNDx.MINUS(0)</t>
+  </si>
+  <si>
+    <t>Floating pin VI__CAPGD.PLUS(59)</t>
+  </si>
+  <si>
+    <t>Xsim_CAPACITORGOODpuget_ROW8</t>
+  </si>
+  <si>
+    <t>Floating pin XCAPACITORGOODpuget1.ok_capacitorgood(ok_capacitorgood)</t>
+  </si>
+  <si>
+    <t>Floating pin XCAPACITORGOODpuget1.status_chrg_status_xdatamap1_6aa5ac6c(status_chrg_status_xdatamap1_6aa5ac6c)</t>
+  </si>
+  <si>
+    <t>Floating pin XFORCE_CAPACITORGOODpuget1.GND(GND)</t>
+  </si>
+  <si>
+    <t>Floating pin XFORCE_CAPACITORGOODpuget1.register_enable_capacitorgood_xd_enable_capacitorgood_32c14a0d(register_enable_capacitorgood_xd_enable_capacitorgood_32c14a0d)</t>
+  </si>
+  <si>
+    <t>Floating Outputs</t>
+  </si>
+  <si>
+    <t>No Connects - Customer</t>
+  </si>
+  <si>
+    <t>No Connects - Celera</t>
+  </si>
+  <si>
     <t>XCAPACITORGOODpuget1,XDEBUG</t>
   </si>
   <si>
-    <t>Floating pin XDEBUG.dft_startup(dft_startup)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.dft_capdetect(dft_capdetect)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.dft_risedelay(dft_risedelay)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.DFT_CAPREFinput(DFT_CAPREFinput)</t>
-  </si>
-  <si>
-    <t>Floating pin V_GNDx.MINUS(0)</t>
-  </si>
-  <si>
-    <t>Floating pin VI__CAPGD.PLUS(59)</t>
-  </si>
-  <si>
-    <t>Xsim_CAPACITORGOODpuget_ROW8</t>
-  </si>
-  <si>
-    <t>Floating pin XCAPACITORGOODpuget1.ok_capacitorgood(ok_capacitorgood)</t>
-  </si>
-  <si>
-    <t>Floating pin XCAPACITORGOODpuget1.status_chrg_status_xdatamap1_6aa5ac6c(status_chrg_status_xdatamap1_6aa5ac6c)</t>
-  </si>
-  <si>
-    <t>Floating pin XFORCE_CAPACITORGOODpuget1.GND(GND)</t>
-  </si>
-  <si>
-    <t>Floating pin XFORCE_CAPACITORGOODpuget1.register_enable_capacitorgood_xd_enable_capacitorgood_32c14a0d(register_enable_capacitorgood_xd_enable_capacitorgood_32c14a0d)</t>
-  </si>
-  <si>
-    <t>Floating Outputs</t>
-  </si>
-  <si>
-    <t>No Connects - Customer</t>
-  </si>
-  <si>
-    <t>No Connects - Celera</t>
+    <t>XDEBUG.dft_startup net: dft_startup io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_capdetect net: dft_capdetect io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_risedelay net: dft_risedelay io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.DFT_CAPREFinput net: DFT_CAPREFinput io: input</t>
   </si>
   <si>
     <t>XIP.IN net: noconn_IN io: output</t>
@@ -978,7 +978,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -998,32 +998,32 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -1036,69 +1036,119 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>19</v>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -1108,52 +1158,22 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1164,49 +1184,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>